--- a/_Learn/Packaging.tutorial/OS.11/24H2/Expand/Install/Report/ar-sa.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/24H2/Expand/Install/Report/ar-sa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\24H2\Expand\Install\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5924f5d6bcb7c7fc/Documents/_Learn/Packaging.tutorial/OS.11/24H2/Expand/Install/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CF82F6-A03B-4206-BA50-70EAD589B531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B6CF82F6-A03B-4206-BA50-70EAD589B531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D2527CB-572D-4478-AC90-885E1558741E}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="5" r:id="rId1"/>
@@ -4762,22 +4762,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.3984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.53125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="120.6640625" style="3" customWidth="1"/>
-    <col min="8" max="10" width="16.6640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.1328125" style="1" hidden="1"/>
+    <col min="1" max="1" width="2.69140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="84.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.3828125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.53515625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="120.69140625" style="3" customWidth="1"/>
+    <col min="8" max="10" width="16.69140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.69140625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="2.69140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.15234375" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4790,7 +4790,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="80.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
       <c r="C2" s="4" t="s">
         <v>257</v>
@@ -4806,7 +4806,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="C3" s="6"/>
       <c r="D3" s="5"/>
@@ -4818,7 +4818,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -4829,7 +4829,7 @@
       <c r="I4" s="10"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="62.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
         <v>8</v>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:12" ht="126" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" ht="126.9" x14ac:dyDescent="0.4">
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="s">
         <v>269</v>
@@ -4889,7 +4889,7 @@
       <c r="K6" s="13"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" ht="110.25" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="111" x14ac:dyDescent="0.4">
       <c r="B7" s="13"/>
       <c r="C7" s="45" t="s">
         <v>268</v>
@@ -4918,17 +4918,13 @@
       <c r="K7" s="46"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:12" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" s="14" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="7"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-    </row>
-    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="9" spans="1:12" s="3" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="7"/>
       <c r="B9" s="16"/>
       <c r="C9" s="17" t="s">
         <v>2</v>
@@ -4937,7 +4933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:12" s="7" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="19"/>
       <c r="C10" s="20" t="s">
         <v>0</v>
@@ -4945,14 +4941,8 @@
       <c r="D10" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="11" spans="1:12" s="7" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="21"/>
       <c r="C11" s="20" t="s">
         <v>1</v>
@@ -4960,31 +4950,20 @@
       <c r="D11" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:12" s="7" customFormat="1" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="3"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4995,7 +4974,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -5006,7 +4985,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -5017,7 +4996,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -5028,7 +5007,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -5039,7 +5018,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -5050,7 +5029,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -5061,7 +5040,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -5072,7 +5051,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -5083,7 +5062,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -5094,7 +5073,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -5105,7 +5084,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -5116,7 +5095,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -5127,7 +5106,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -5138,7 +5117,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -5149,7 +5128,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -5160,7 +5139,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -5171,7 +5150,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -5182,7 +5161,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -5193,7 +5172,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -5204,7 +5183,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -5221,7 +5200,7 @@
   <mergeCells count="1">
     <mergeCell ref="F2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F8:I1048576 F1:I4 H5:J5">
+  <conditionalFormatting sqref="F13:I1048576 F1:I4 H5:J5">
     <cfRule type="iconSet" priority="282">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
@@ -5240,7 +5219,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:I8 H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5266,29 +5245,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="13" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="14" max="15" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="16" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>256</v>
       </c>
@@ -5296,7 +5275,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -5304,7 +5283,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>70</v>
@@ -5312,7 +5291,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>15</v>
@@ -5320,13 +5299,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>70</v>
       </c>
@@ -5334,7 +5313,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>6</v>
@@ -5349,7 +5328,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -5363,7 +5342,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -5377,7 +5356,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -5391,7 +5370,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -5405,7 +5384,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -5419,7 +5398,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -5433,7 +5412,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -5447,7 +5426,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -5461,7 +5440,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -5475,7 +5454,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -5489,7 +5468,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -5503,7 +5482,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -5517,7 +5496,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -5531,7 +5510,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -5545,7 +5524,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -5559,7 +5538,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -5573,7 +5552,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -5587,7 +5566,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -5601,7 +5580,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -5615,7 +5594,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -5629,7 +5608,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -5643,7 +5622,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -5657,7 +5636,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -5671,7 +5650,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -5685,7 +5664,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -5699,7 +5678,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -5713,7 +5692,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -5727,7 +5706,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -5741,7 +5720,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -5755,7 +5734,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -5769,7 +5748,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -5783,7 +5762,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -5797,7 +5776,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -5811,7 +5790,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -5825,7 +5804,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -5839,7 +5818,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -5853,7 +5832,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -5867,7 +5846,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -5881,7 +5860,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -5895,7 +5874,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -5909,7 +5888,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -5923,7 +5902,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -5937,7 +5916,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -5951,7 +5930,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -5965,7 +5944,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -5979,7 +5958,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -5993,7 +5972,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -6007,7 +5986,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="56" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3">
         <v>48</v>
       </c>
@@ -6021,17 +6000,17 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D57" s="14"/>
       <c r="E57" s="28"/>
       <c r="F57" s="15"/>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="33" t="s">
         <v>6</v>
       </c>
@@ -6045,7 +6024,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="35">
         <v>1</v>
       </c>
@@ -6059,7 +6038,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="38">
         <v>2</v>
       </c>
@@ -6073,7 +6052,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="35">
         <v>3</v>
       </c>
@@ -6087,7 +6066,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="38">
         <v>4</v>
       </c>
@@ -6101,7 +6080,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="35">
         <v>5</v>
       </c>
@@ -6115,7 +6094,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C65" s="38">
         <v>6</v>
       </c>
@@ -6129,7 +6108,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C66" s="35">
         <v>7</v>
       </c>
@@ -6143,7 +6122,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C67" s="38">
         <v>8</v>
       </c>
@@ -6157,7 +6136,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C68" s="35">
         <v>9</v>
       </c>
@@ -6171,7 +6150,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C69" s="38">
         <v>10</v>
       </c>
@@ -6185,7 +6164,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C70" s="35">
         <v>11</v>
       </c>
@@ -6199,7 +6178,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C71" s="38">
         <v>12</v>
       </c>
@@ -6213,7 +6192,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C72" s="35">
         <v>13</v>
       </c>
@@ -6227,7 +6206,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C73" s="38">
         <v>14</v>
       </c>
@@ -6241,7 +6220,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C74" s="35">
         <v>15</v>
       </c>
@@ -6255,7 +6234,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C75" s="38">
         <v>16</v>
       </c>
@@ -6269,7 +6248,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C76" s="35">
         <v>17</v>
       </c>
@@ -6283,7 +6262,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C77" s="38">
         <v>18</v>
       </c>
@@ -6297,7 +6276,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C78" s="35">
         <v>19</v>
       </c>
@@ -6311,7 +6290,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C79" s="38">
         <v>20</v>
       </c>
@@ -6325,7 +6304,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C80" s="35">
         <v>21</v>
       </c>
@@ -6339,7 +6318,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C81" s="38">
         <v>22</v>
       </c>
@@ -6353,7 +6332,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C82" s="35">
         <v>23</v>
       </c>
@@ -6367,7 +6346,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C83" s="38">
         <v>24</v>
       </c>
@@ -6381,7 +6360,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C84" s="35">
         <v>25</v>
       </c>
@@ -6395,7 +6374,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C85" s="38">
         <v>26</v>
       </c>
@@ -6409,7 +6388,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C86" s="35">
         <v>27</v>
       </c>
@@ -6423,7 +6402,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C87" s="38">
         <v>28</v>
       </c>
@@ -6437,7 +6416,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C88" s="35">
         <v>29</v>
       </c>
@@ -6451,7 +6430,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C89" s="38">
         <v>30</v>
       </c>
@@ -6465,7 +6444,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C90" s="35">
         <v>31</v>
       </c>
@@ -6479,7 +6458,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C91" s="38">
         <v>32</v>
       </c>
@@ -6493,7 +6472,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C92" s="35">
         <v>33</v>
       </c>
@@ -6507,7 +6486,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C93" s="38">
         <v>34</v>
       </c>
@@ -6521,7 +6500,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C94" s="35">
         <v>35</v>
       </c>
@@ -6535,7 +6514,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C95" s="38">
         <v>36</v>
       </c>
@@ -6549,7 +6528,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C96" s="35">
         <v>37</v>
       </c>
@@ -6563,7 +6542,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C97" s="38">
         <v>38</v>
       </c>
@@ -6577,7 +6556,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C98" s="35">
         <v>39</v>
       </c>
@@ -6591,7 +6570,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C99" s="38">
         <v>40</v>
       </c>
@@ -6605,7 +6584,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C100" s="35">
         <v>41</v>
       </c>
@@ -6619,7 +6598,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C101" s="38">
         <v>42</v>
       </c>
@@ -6633,7 +6612,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C102" s="35">
         <v>43</v>
       </c>
@@ -6647,7 +6626,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C103" s="38">
         <v>44</v>
       </c>
@@ -6661,7 +6640,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C104" s="35">
         <v>45</v>
       </c>
@@ -6675,7 +6654,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C105" s="38">
         <v>46</v>
       </c>
@@ -6689,7 +6668,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C106" s="35">
         <v>47</v>
       </c>
@@ -6703,7 +6682,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C107" s="38">
         <v>48</v>
       </c>
@@ -6717,7 +6696,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C108" s="35">
         <v>49</v>
       </c>
@@ -6731,7 +6710,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C109" s="38">
         <v>50</v>
       </c>
@@ -6745,7 +6724,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C110" s="35">
         <v>51</v>
       </c>
@@ -6759,7 +6738,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C111" s="38">
         <v>52</v>
       </c>
@@ -6773,7 +6752,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C112" s="35">
         <v>53</v>
       </c>
@@ -6787,7 +6766,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C113" s="38">
         <v>54</v>
       </c>
@@ -6801,7 +6780,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C114" s="35">
         <v>55</v>
       </c>
@@ -6815,7 +6794,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C115" s="38">
         <v>56</v>
       </c>
@@ -6829,7 +6808,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C116" s="35">
         <v>57</v>
       </c>
@@ -6843,7 +6822,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C117" s="38">
         <v>58</v>
       </c>
@@ -6857,7 +6836,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C118" s="35">
         <v>59</v>
       </c>
@@ -6871,7 +6850,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C119" s="38">
         <v>60</v>
       </c>
@@ -6885,7 +6864,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C120" s="35">
         <v>61</v>
       </c>
@@ -6899,7 +6878,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C121" s="38">
         <v>62</v>
       </c>
@@ -6913,7 +6892,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C122" s="35">
         <v>63</v>
       </c>
@@ -6927,7 +6906,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C123" s="38">
         <v>64</v>
       </c>
@@ -6941,7 +6920,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C124" s="35">
         <v>65</v>
       </c>
@@ -6955,7 +6934,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C125" s="38">
         <v>66</v>
       </c>
@@ -6969,7 +6948,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C126" s="35">
         <v>67</v>
       </c>
@@ -6983,7 +6962,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C127" s="38">
         <v>68</v>
       </c>
@@ -6997,7 +6976,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C128" s="35">
         <v>69</v>
       </c>
@@ -7011,7 +6990,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C129" s="38">
         <v>70</v>
       </c>
@@ -7025,7 +7004,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C130" s="35">
         <v>71</v>
       </c>
@@ -7039,7 +7018,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C131" s="38">
         <v>72</v>
       </c>
@@ -7053,7 +7032,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C132" s="35">
         <v>73</v>
       </c>
@@ -7067,7 +7046,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="38">
         <v>74</v>
       </c>
@@ -7081,7 +7060,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="35">
         <v>75</v>
       </c>
@@ -7095,7 +7074,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="38">
         <v>76</v>
       </c>
@@ -7109,7 +7088,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="3">
         <v>77</v>
       </c>
@@ -7123,7 +7102,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="137" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="38">
         <v>78</v>
       </c>
@@ -7137,7 +7116,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="138" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="3">
         <v>79</v>
       </c>
@@ -7174,29 +7153,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>262</v>
       </c>
@@ -7204,7 +7183,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -7212,7 +7191,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>70</v>
@@ -7220,7 +7199,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>15</v>
@@ -7228,13 +7207,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>70</v>
       </c>
@@ -7242,7 +7221,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>6</v>
@@ -7257,7 +7236,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -7271,7 +7250,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -7285,7 +7264,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -7299,7 +7278,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -7313,7 +7292,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -7327,7 +7306,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -7341,7 +7320,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -7355,7 +7334,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -7369,7 +7348,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -7383,7 +7362,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -7397,7 +7376,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -7411,7 +7390,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -7425,7 +7404,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -7439,7 +7418,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -7453,7 +7432,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -7467,7 +7446,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -7481,7 +7460,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -7495,7 +7474,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -7509,7 +7488,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -7523,7 +7502,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -7537,7 +7516,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -7551,7 +7530,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -7565,7 +7544,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -7579,7 +7558,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -7593,7 +7572,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -7607,7 +7586,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -7621,7 +7600,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -7635,7 +7614,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -7649,7 +7628,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -7663,7 +7642,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -7677,7 +7656,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -7691,7 +7670,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -7705,7 +7684,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -7719,7 +7698,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -7733,7 +7712,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -7747,7 +7726,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -7761,7 +7740,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -7775,7 +7754,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -7789,7 +7768,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -7803,7 +7782,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -7817,7 +7796,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -7831,7 +7810,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -7845,7 +7824,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -7859,7 +7838,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -7873,7 +7852,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -7887,7 +7866,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="54" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -7901,7 +7880,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -7915,7 +7894,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="56" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3">
         <v>48</v>
       </c>
@@ -7929,17 +7908,17 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D57" s="14"/>
       <c r="E57" s="28"/>
       <c r="F57" s="13"/>
     </row>
-    <row r="58" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="33" t="s">
         <v>6</v>
       </c>
@@ -7953,7 +7932,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B60" s="41"/>
       <c r="C60" s="37">
         <v>1</v>
@@ -7968,7 +7947,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B61" s="41"/>
       <c r="C61" s="40">
         <v>2</v>
@@ -7983,7 +7962,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B62" s="41"/>
       <c r="C62" s="37">
         <v>3</v>
@@ -7998,7 +7977,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B63" s="41"/>
       <c r="C63" s="40">
         <v>4</v>
@@ -8013,7 +7992,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B64" s="41"/>
       <c r="C64" s="37">
         <v>5</v>
@@ -8028,7 +8007,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B65" s="41"/>
       <c r="C65" s="40">
         <v>6</v>
@@ -8043,7 +8022,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B66" s="41"/>
       <c r="C66" s="37">
         <v>7</v>
@@ -8058,7 +8037,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B67" s="41"/>
       <c r="C67" s="40">
         <v>8</v>
@@ -8073,7 +8052,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B68" s="41"/>
       <c r="C68" s="37">
         <v>9</v>
@@ -8088,7 +8067,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B69" s="41"/>
       <c r="C69" s="40">
         <v>10</v>
@@ -8103,7 +8082,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="41"/>
       <c r="C70" s="37">
         <v>11</v>
@@ -8118,7 +8097,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B71" s="41"/>
       <c r="C71" s="40">
         <v>12</v>
@@ -8133,7 +8112,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B72" s="41"/>
       <c r="C72" s="37">
         <v>13</v>
@@ -8148,7 +8127,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B73" s="41"/>
       <c r="C73" s="40">
         <v>14</v>
@@ -8163,7 +8142,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B74" s="41"/>
       <c r="C74" s="37">
         <v>15</v>
@@ -8178,7 +8157,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B75" s="41"/>
       <c r="C75" s="40">
         <v>16</v>
@@ -8193,7 +8172,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B76" s="41"/>
       <c r="C76" s="37">
         <v>17</v>
@@ -8208,7 +8187,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="77" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B77" s="41"/>
       <c r="C77" s="40">
         <v>18</v>
@@ -8223,7 +8202,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="78" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B78" s="41"/>
       <c r="C78" s="37">
         <v>19</v>
@@ -8238,7 +8217,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C79" s="38">
         <v>20</v>
       </c>
@@ -8252,7 +8231,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C80" s="35">
         <v>21</v>
       </c>
@@ -8266,7 +8245,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C81" s="38">
         <v>22</v>
       </c>
@@ -8280,7 +8259,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C82" s="35">
         <v>23</v>
       </c>
@@ -8294,7 +8273,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C83" s="38">
         <v>24</v>
       </c>
@@ -8308,7 +8287,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C84" s="35">
         <v>25</v>
       </c>
@@ -8322,7 +8301,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C85" s="38">
         <v>26</v>
       </c>
@@ -8336,7 +8315,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C86" s="35">
         <v>27</v>
       </c>
@@ -8350,7 +8329,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C87" s="38">
         <v>28</v>
       </c>
@@ -8364,7 +8343,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C88" s="35">
         <v>29</v>
       </c>
@@ -8378,7 +8357,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C89" s="38">
         <v>30</v>
       </c>
@@ -8392,7 +8371,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C90" s="35">
         <v>31</v>
       </c>
@@ -8406,7 +8385,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C91" s="38">
         <v>32</v>
       </c>
@@ -8420,7 +8399,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C92" s="35">
         <v>33</v>
       </c>
@@ -8434,7 +8413,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C93" s="38">
         <v>34</v>
       </c>
@@ -8448,7 +8427,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C94" s="35">
         <v>35</v>
       </c>
@@ -8462,7 +8441,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C95" s="38">
         <v>36</v>
       </c>
@@ -8476,7 +8455,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C96" s="35">
         <v>37</v>
       </c>
@@ -8490,7 +8469,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C97" s="38">
         <v>38</v>
       </c>
@@ -8504,7 +8483,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C98" s="35">
         <v>39</v>
       </c>
@@ -8518,7 +8497,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C99" s="38">
         <v>40</v>
       </c>
@@ -8532,7 +8511,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C100" s="35">
         <v>41</v>
       </c>
@@ -8546,7 +8525,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C101" s="38">
         <v>42</v>
       </c>
@@ -8560,7 +8539,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C102" s="35">
         <v>43</v>
       </c>
@@ -8574,7 +8553,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C103" s="38">
         <v>44</v>
       </c>
@@ -8588,7 +8567,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C104" s="35">
         <v>45</v>
       </c>
@@ -8602,7 +8581,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C105" s="38">
         <v>46</v>
       </c>
@@ -8616,7 +8595,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C106" s="35">
         <v>47</v>
       </c>
@@ -8630,7 +8609,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C107" s="38">
         <v>48</v>
       </c>
@@ -8644,7 +8623,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C108" s="35">
         <v>49</v>
       </c>
@@ -8658,7 +8637,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C109" s="38">
         <v>50</v>
       </c>
@@ -8672,7 +8651,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C110" s="35">
         <v>51</v>
       </c>
@@ -8686,7 +8665,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C111" s="38">
         <v>52</v>
       </c>
@@ -8700,7 +8679,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C112" s="35">
         <v>53</v>
       </c>
@@ -8714,7 +8693,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C113" s="38">
         <v>54</v>
       </c>
@@ -8728,7 +8707,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C114" s="35">
         <v>55</v>
       </c>
@@ -8742,7 +8721,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C115" s="38">
         <v>56</v>
       </c>
@@ -8756,7 +8735,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C116" s="35">
         <v>57</v>
       </c>
@@ -8770,7 +8749,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C117" s="38">
         <v>58</v>
       </c>
@@ -8784,7 +8763,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C118" s="35">
         <v>59</v>
       </c>
@@ -8798,7 +8777,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C119" s="38">
         <v>60</v>
       </c>
@@ -8812,7 +8791,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C120" s="35">
         <v>61</v>
       </c>
@@ -8826,7 +8805,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C121" s="38">
         <v>62</v>
       </c>
@@ -8840,7 +8819,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C122" s="35">
         <v>63</v>
       </c>
@@ -8854,7 +8833,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C123" s="38">
         <v>64</v>
       </c>
@@ -8868,7 +8847,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C124" s="35">
         <v>65</v>
       </c>
@@ -8882,7 +8861,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C125" s="38">
         <v>66</v>
       </c>
@@ -8896,7 +8875,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C126" s="35">
         <v>67</v>
       </c>
@@ -8910,7 +8889,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C127" s="38">
         <v>68</v>
       </c>
@@ -8924,7 +8903,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C128" s="35">
         <v>69</v>
       </c>
@@ -8938,7 +8917,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C129" s="38">
         <v>70</v>
       </c>
@@ -8952,7 +8931,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C130" s="35">
         <v>71</v>
       </c>
@@ -8966,7 +8945,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C131" s="38">
         <v>72</v>
       </c>
@@ -8980,7 +8959,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C132" s="35">
         <v>73</v>
       </c>
@@ -8994,7 +8973,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="38">
         <v>74</v>
       </c>
@@ -9008,7 +8987,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="35">
         <v>75</v>
       </c>
@@ -9022,7 +9001,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="38">
         <v>76</v>
       </c>
@@ -9036,7 +9015,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="3">
         <v>77</v>
       </c>
@@ -9050,7 +9029,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="137" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="38">
         <v>78</v>
       </c>
@@ -9064,7 +9043,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="138" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="3">
         <v>79</v>
       </c>
@@ -9101,29 +9080,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R139"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>263</v>
       </c>
@@ -9131,7 +9110,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -9139,7 +9118,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>70</v>
@@ -9147,7 +9126,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>15</v>
@@ -9155,13 +9134,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>70</v>
       </c>
@@ -9169,7 +9148,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>6</v>
@@ -9184,7 +9163,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -9198,7 +9177,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -9212,7 +9191,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -9226,7 +9205,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -9240,7 +9219,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -9254,7 +9233,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -9268,7 +9247,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -9282,7 +9261,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -9296,7 +9275,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -9310,7 +9289,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -9324,7 +9303,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -9338,7 +9317,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -9352,7 +9331,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -9366,7 +9345,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -9380,7 +9359,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -9394,7 +9373,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -9408,7 +9387,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -9422,7 +9401,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -9436,7 +9415,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -9450,7 +9429,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -9464,7 +9443,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -9478,7 +9457,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -9492,7 +9471,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -9506,7 +9485,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -9520,7 +9499,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -9534,7 +9513,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -9548,7 +9527,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -9562,7 +9541,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -9576,7 +9555,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -9590,7 +9569,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -9604,7 +9583,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -9618,7 +9597,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -9632,7 +9611,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -9646,7 +9625,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -9660,7 +9639,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -9674,7 +9653,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -9688,7 +9667,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -9702,7 +9681,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -9716,7 +9695,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -9730,7 +9709,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -9744,7 +9723,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -9758,7 +9737,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -9772,7 +9751,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -9786,7 +9765,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -9800,7 +9779,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -9814,7 +9793,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -9828,7 +9807,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -9842,17 +9821,17 @@
         <v>113</v>
       </c>
     </row>
-    <row r="56" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D56" s="14"/>
       <c r="E56" s="28"/>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="33" t="s">
         <v>6</v>
       </c>
@@ -9866,7 +9845,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="35">
         <v>1</v>
       </c>
@@ -9880,7 +9859,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="38">
         <v>2</v>
       </c>
@@ -9894,7 +9873,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="35">
         <v>3</v>
       </c>
@@ -9908,7 +9887,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="38">
         <v>4</v>
       </c>
@@ -9922,7 +9901,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="35">
         <v>5</v>
       </c>
@@ -9936,7 +9915,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="38">
         <v>6</v>
       </c>
@@ -9950,7 +9929,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="35">
@@ -9971,7 +9950,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="38">
@@ -9992,7 +9971,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="35">
@@ -10013,7 +9992,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="38">
@@ -10034,7 +10013,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="35">
@@ -10055,7 +10034,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="38">
@@ -10076,7 +10055,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="35">
@@ -10097,7 +10076,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="38">
@@ -10118,7 +10097,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="35">
@@ -10139,7 +10118,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="38">
@@ -10160,7 +10139,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="35">
@@ -10181,7 +10160,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="38">
@@ -10202,7 +10181,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="35">
@@ -10223,7 +10202,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="38">
@@ -10244,7 +10223,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="35">
@@ -10265,7 +10244,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="38">
@@ -10286,7 +10265,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="35">
@@ -10307,7 +10286,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="38">
@@ -10328,7 +10307,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="35">
@@ -10349,7 +10328,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="38">
@@ -10370,7 +10349,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="35">
@@ -10391,7 +10370,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="38">
@@ -10412,7 +10391,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="35">
@@ -10433,7 +10412,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="38">
@@ -10454,7 +10433,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="35">
@@ -10475,7 +10454,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="38">
@@ -10496,7 +10475,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="35">
@@ -10517,7 +10496,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="38">
@@ -10538,7 +10517,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="35">
@@ -10559,7 +10538,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="38">
@@ -10580,7 +10559,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="35">
@@ -10601,7 +10580,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="38">
@@ -10622,7 +10601,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="35">
@@ -10643,7 +10622,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="38">
@@ -10664,7 +10643,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="35">
@@ -10685,7 +10664,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="38">
@@ -10706,7 +10685,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="35">
@@ -10727,7 +10706,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="38">
@@ -10748,7 +10727,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="35">
@@ -10769,7 +10748,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="38">
@@ -10790,7 +10769,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="35">
@@ -10811,7 +10790,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="38">
@@ -10832,7 +10811,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="35">
@@ -10853,7 +10832,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="38">
@@ -10874,7 +10853,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="35">
@@ -10895,7 +10874,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="38">
@@ -10916,7 +10895,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="35">
@@ -10937,7 +10916,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="38">
@@ -10958,7 +10937,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="35">
@@ -10979,7 +10958,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="38">
@@ -11000,7 +10979,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="35">
@@ -11021,7 +11000,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="38">
@@ -11042,7 +11021,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="35">
@@ -11063,7 +11042,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="38">
@@ -11084,7 +11063,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="35">
@@ -11105,7 +11084,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="38">
@@ -11126,7 +11105,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="35">
@@ -11147,7 +11126,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="38">
@@ -11168,7 +11147,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="35">
@@ -11189,7 +11168,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="38">
@@ -11210,7 +11189,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="35">
@@ -11231,7 +11210,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="38">
@@ -11252,7 +11231,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="35">
@@ -11273,7 +11252,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="38">
@@ -11294,7 +11273,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="35">
@@ -11315,7 +11294,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="38">
@@ -11336,7 +11315,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="35">
@@ -11357,7 +11336,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="38">
@@ -11378,7 +11357,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="29"/>
       <c r="B133" s="27"/>
       <c r="C133" s="35">
@@ -11399,7 +11378,7 @@
       <c r="J133" s="29"/>
       <c r="K133" s="29"/>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="38">
         <v>76</v>
       </c>
@@ -11413,7 +11392,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="35">
         <v>77</v>
       </c>
@@ -11427,7 +11406,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="38">
         <v>78</v>
       </c>
@@ -11441,7 +11420,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>79</v>
       </c>
@@ -11455,7 +11434,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="38">
         <v>80</v>
       </c>
@@ -11469,7 +11448,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C139" s="3">
         <v>81</v>
       </c>
@@ -11506,29 +11485,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R139"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>264</v>
       </c>
@@ -11536,7 +11515,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -11544,7 +11523,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>70</v>
@@ -11552,7 +11531,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>15</v>
@@ -11560,13 +11539,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>70</v>
       </c>
@@ -11574,7 +11553,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>6</v>
@@ -11589,7 +11568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -11603,7 +11582,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -11617,7 +11596,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -11631,7 +11610,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -11645,7 +11624,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -11659,7 +11638,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -11673,7 +11652,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -11687,7 +11666,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -11701,7 +11680,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -11715,7 +11694,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -11729,7 +11708,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -11743,7 +11722,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -11757,7 +11736,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -11771,7 +11750,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -11785,7 +11764,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -11799,7 +11778,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -11813,7 +11792,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -11827,7 +11806,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -11841,7 +11820,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -11855,7 +11834,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -11869,7 +11848,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -11883,7 +11862,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -11897,7 +11876,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -11911,7 +11890,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -11925,7 +11904,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -11939,7 +11918,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -11953,7 +11932,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -11967,7 +11946,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -11981,7 +11960,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -11995,7 +11974,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -12009,7 +11988,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -12023,7 +12002,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -12037,7 +12016,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -12051,7 +12030,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -12065,7 +12044,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -12079,7 +12058,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -12093,7 +12072,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -12107,7 +12086,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -12121,7 +12100,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -12135,7 +12114,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -12149,7 +12128,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -12163,7 +12142,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -12177,7 +12156,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -12191,7 +12170,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -12205,7 +12184,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -12219,7 +12198,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -12233,7 +12212,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -12247,17 +12226,17 @@
         <v>113</v>
       </c>
     </row>
-    <row r="56" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D56" s="14"/>
       <c r="E56" s="28"/>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="33" t="s">
         <v>6</v>
       </c>
@@ -12271,7 +12250,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="35">
         <v>1</v>
       </c>
@@ -12285,7 +12264,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="38">
         <v>2</v>
       </c>
@@ -12299,7 +12278,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="35">
         <v>3</v>
       </c>
@@ -12313,7 +12292,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="38">
         <v>4</v>
       </c>
@@ -12327,7 +12306,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="35">
         <v>5</v>
       </c>
@@ -12341,7 +12320,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="38">
         <v>6</v>
       </c>
@@ -12355,7 +12334,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="35">
@@ -12376,7 +12355,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="38">
@@ -12397,7 +12376,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="35">
@@ -12418,7 +12397,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="38">
@@ -12439,7 +12418,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="35">
@@ -12460,7 +12439,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="38">
@@ -12481,7 +12460,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="35">
@@ -12502,7 +12481,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="38">
@@ -12523,7 +12502,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="35">
@@ -12544,7 +12523,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="38">
@@ -12565,7 +12544,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="35">
@@ -12586,7 +12565,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="38">
@@ -12607,7 +12586,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="35">
@@ -12628,7 +12607,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="38">
@@ -12649,7 +12628,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="35">
@@ -12670,7 +12649,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="38">
@@ -12691,7 +12670,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="35">
@@ -12712,7 +12691,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="38">
@@ -12733,7 +12712,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="35">
@@ -12754,7 +12733,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="38">
@@ -12775,7 +12754,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="35">
@@ -12796,7 +12775,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="38">
@@ -12817,7 +12796,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="35">
@@ -12838,7 +12817,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="38">
@@ -12859,7 +12838,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="35">
@@ -12880,7 +12859,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="38">
@@ -12901,7 +12880,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="35">
@@ -12922,7 +12901,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="38">
@@ -12943,7 +12922,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="35">
@@ -12964,7 +12943,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="38">
@@ -12985,7 +12964,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="35">
@@ -13006,7 +12985,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="38">
@@ -13027,7 +13006,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="35">
@@ -13048,7 +13027,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="38">
@@ -13069,7 +13048,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="35">
@@ -13090,7 +13069,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="38">
@@ -13111,7 +13090,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="35">
@@ -13132,7 +13111,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="38">
@@ -13153,7 +13132,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="35">
@@ -13174,7 +13153,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="38">
@@ -13195,7 +13174,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="35">
@@ -13216,7 +13195,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="38">
@@ -13237,7 +13216,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="35">
@@ -13258,7 +13237,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="38">
@@ -13279,7 +13258,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="35">
@@ -13300,7 +13279,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="38">
@@ -13321,7 +13300,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="35">
@@ -13342,7 +13321,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="38">
@@ -13363,7 +13342,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="35">
@@ -13384,7 +13363,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="38">
@@ -13405,7 +13384,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="35">
@@ -13426,7 +13405,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="38">
@@ -13447,7 +13426,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="35">
@@ -13468,7 +13447,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="38">
@@ -13489,7 +13468,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="35">
@@ -13510,7 +13489,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="38">
@@ -13531,7 +13510,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="35">
@@ -13552,7 +13531,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="38">
@@ -13573,7 +13552,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="35">
@@ -13594,7 +13573,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="38">
@@ -13615,7 +13594,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="35">
@@ -13636,7 +13615,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="38">
@@ -13657,7 +13636,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="35">
@@ -13678,7 +13657,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="38">
@@ -13699,7 +13678,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="35">
@@ -13720,7 +13699,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="38">
@@ -13741,7 +13720,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="35">
@@ -13762,7 +13741,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="38">
@@ -13783,7 +13762,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="29"/>
       <c r="B133" s="27"/>
       <c r="C133" s="35">
@@ -13804,7 +13783,7 @@
       <c r="J133" s="29"/>
       <c r="K133" s="29"/>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="38">
         <v>76</v>
       </c>
@@ -13818,7 +13797,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="35">
         <v>77</v>
       </c>
@@ -13832,7 +13811,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="38">
         <v>78</v>
       </c>
@@ -13846,7 +13825,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>79</v>
       </c>
@@ -13860,7 +13839,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="38">
         <v>80</v>
       </c>
@@ -13874,7 +13853,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C139" s="3">
         <v>81</v>
       </c>
@@ -13911,29 +13890,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R139"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>265</v>
       </c>
@@ -13941,7 +13920,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -13949,7 +13928,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>70</v>
@@ -13957,7 +13936,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>15</v>
@@ -13965,13 +13944,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>70</v>
       </c>
@@ -13979,7 +13958,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>6</v>
@@ -13994,7 +13973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -14008,7 +13987,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -14022,7 +14001,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -14036,7 +14015,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -14050,7 +14029,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -14064,7 +14043,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -14078,7 +14057,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -14092,7 +14071,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -14106,7 +14085,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -14120,7 +14099,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -14134,7 +14113,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -14148,7 +14127,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -14162,7 +14141,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -14176,7 +14155,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -14190,7 +14169,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -14204,7 +14183,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -14218,7 +14197,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -14232,7 +14211,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -14246,7 +14225,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -14260,7 +14239,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -14274,7 +14253,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -14288,7 +14267,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -14302,7 +14281,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -14316,7 +14295,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -14330,7 +14309,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -14344,7 +14323,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -14358,7 +14337,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -14372,7 +14351,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -14386,7 +14365,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -14400,7 +14379,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -14414,7 +14393,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -14428,7 +14407,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -14442,7 +14421,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -14456,7 +14435,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -14470,7 +14449,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -14484,7 +14463,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -14498,7 +14477,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -14512,7 +14491,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -14526,7 +14505,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -14540,7 +14519,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -14554,7 +14533,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -14568,7 +14547,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -14582,7 +14561,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -14596,7 +14575,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -14610,7 +14589,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -14624,7 +14603,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -14638,7 +14617,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -14652,17 +14631,17 @@
         <v>113</v>
       </c>
     </row>
-    <row r="56" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D56" s="14"/>
       <c r="E56" s="28"/>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="33" t="s">
         <v>6</v>
       </c>
@@ -14676,7 +14655,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="35">
         <v>1</v>
       </c>
@@ -14690,7 +14669,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="38">
         <v>2</v>
       </c>
@@ -14704,7 +14683,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="35">
         <v>3</v>
       </c>
@@ -14718,7 +14697,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="38">
         <v>4</v>
       </c>
@@ -14732,7 +14711,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="35">
         <v>5</v>
       </c>
@@ -14746,7 +14725,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="38">
         <v>6</v>
       </c>
@@ -14760,7 +14739,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="35">
@@ -14781,7 +14760,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="38">
@@ -14802,7 +14781,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="35">
@@ -14823,7 +14802,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="38">
@@ -14844,7 +14823,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="35">
@@ -14865,7 +14844,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="38">
@@ -14886,7 +14865,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="35">
@@ -14907,7 +14886,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="38">
@@ -14928,7 +14907,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="35">
@@ -14949,7 +14928,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="38">
@@ -14970,7 +14949,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="35">
@@ -14991,7 +14970,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="38">
@@ -15012,7 +14991,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="35">
@@ -15033,7 +15012,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="38">
@@ -15054,7 +15033,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="35">
@@ -15075,7 +15054,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="38">
@@ -15096,7 +15075,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="35">
@@ -15117,7 +15096,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="38">
@@ -15138,7 +15117,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="35">
@@ -15159,7 +15138,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="38">
@@ -15180,7 +15159,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="35">
@@ -15201,7 +15180,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="38">
@@ -15222,7 +15201,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="35">
@@ -15243,7 +15222,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="38">
@@ -15264,7 +15243,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="35">
@@ -15285,7 +15264,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="38">
@@ -15306,7 +15285,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="35">
@@ -15327,7 +15306,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="38">
@@ -15348,7 +15327,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="35">
@@ -15369,7 +15348,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="38">
@@ -15390,7 +15369,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="35">
@@ -15411,7 +15390,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="38">
@@ -15432,7 +15411,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="35">
@@ -15453,7 +15432,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="38">
@@ -15474,7 +15453,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="35">
@@ -15495,7 +15474,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="38">
@@ -15516,7 +15495,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="35">
@@ -15537,7 +15516,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="38">
@@ -15558,7 +15537,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="35">
@@ -15579,7 +15558,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="38">
@@ -15600,7 +15579,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="35">
@@ -15621,7 +15600,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="38">
@@ -15642,7 +15621,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="35">
@@ -15663,7 +15642,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="38">
@@ -15684,7 +15663,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="35">
@@ -15705,7 +15684,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="38">
@@ -15726,7 +15705,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="35">
@@ -15747,7 +15726,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="38">
@@ -15768,7 +15747,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="35">
@@ -15789,7 +15768,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="38">
@@ -15810,7 +15789,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="35">
@@ -15831,7 +15810,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="38">
@@ -15852,7 +15831,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="35">
@@ -15873,7 +15852,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="38">
@@ -15894,7 +15873,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="35">
@@ -15915,7 +15894,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="38">
@@ -15936,7 +15915,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="35">
@@ -15957,7 +15936,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="38">
@@ -15978,7 +15957,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="35">
@@ -15999,7 +15978,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="38">
@@ -16020,7 +15999,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="35">
@@ -16041,7 +16020,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="38">
@@ -16062,7 +16041,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="35">
@@ -16083,7 +16062,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="38">
@@ -16104,7 +16083,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="35">
@@ -16125,7 +16104,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="38">
@@ -16146,7 +16125,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="35">
@@ -16167,7 +16146,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="38">
@@ -16188,7 +16167,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="29"/>
       <c r="B133" s="27"/>
       <c r="C133" s="35">
@@ -16209,7 +16188,7 @@
       <c r="J133" s="29"/>
       <c r="K133" s="29"/>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="38">
         <v>76</v>
       </c>
@@ -16223,7 +16202,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="35">
         <v>77</v>
       </c>
@@ -16237,7 +16216,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="3">
         <v>78</v>
       </c>
@@ -16251,7 +16230,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>79</v>
       </c>
@@ -16265,7 +16244,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="3">
         <v>80</v>
       </c>
@@ -16279,7 +16258,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C139" s="3">
         <v>81</v>
       </c>
@@ -16316,29 +16295,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R139"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="12" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="13" max="14" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="15" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>266</v>
       </c>
@@ -16346,7 +16325,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -16354,7 +16333,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>70</v>
@@ -16362,7 +16341,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>15</v>
@@ -16370,13 +16349,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>70</v>
       </c>
@@ -16384,7 +16363,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>6</v>
@@ -16399,7 +16378,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -16413,7 +16392,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -16427,7 +16406,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -16441,7 +16420,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -16455,7 +16434,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -16469,7 +16448,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -16483,7 +16462,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -16497,7 +16476,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -16511,7 +16490,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -16525,7 +16504,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -16539,7 +16518,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -16553,7 +16532,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -16567,7 +16546,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -16581,7 +16560,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -16595,7 +16574,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -16609,7 +16588,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -16623,7 +16602,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -16637,7 +16616,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -16651,7 +16630,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -16665,7 +16644,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -16679,7 +16658,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -16693,7 +16672,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -16707,7 +16686,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -16721,7 +16700,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -16735,7 +16714,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -16749,7 +16728,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -16763,7 +16742,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -16777,7 +16756,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -16791,7 +16770,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -16805,7 +16784,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -16819,7 +16798,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -16833,7 +16812,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -16847,7 +16826,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -16861,7 +16840,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -16875,7 +16854,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -16889,7 +16868,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -16903,7 +16882,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -16917,7 +16896,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -16931,7 +16910,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -16945,7 +16924,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -16959,7 +16938,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -16973,7 +16952,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -16987,7 +16966,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -17001,7 +16980,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -17015,7 +16994,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -17029,7 +17008,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -17043,7 +17022,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -17057,17 +17036,17 @@
         <v>113</v>
       </c>
     </row>
-    <row r="56" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D56" s="14"/>
       <c r="E56" s="28"/>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="33" t="s">
         <v>6</v>
       </c>
@@ -17081,7 +17060,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="35">
         <v>1</v>
       </c>
@@ -17095,7 +17074,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="38">
         <v>2</v>
       </c>
@@ -17109,7 +17088,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="35">
         <v>3</v>
       </c>
@@ -17123,7 +17102,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="38">
         <v>4</v>
       </c>
@@ -17137,7 +17116,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="35">
         <v>5</v>
       </c>
@@ -17151,7 +17130,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="38">
         <v>6</v>
       </c>
@@ -17165,7 +17144,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="35">
@@ -17185,7 +17164,7 @@
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="38">
@@ -17205,7 +17184,7 @@
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="35">
@@ -17225,7 +17204,7 @@
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="38">
@@ -17245,7 +17224,7 @@
       <c r="I68" s="29"/>
       <c r="J68" s="29"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="35">
@@ -17265,7 +17244,7 @@
       <c r="I69" s="29"/>
       <c r="J69" s="29"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="38">
@@ -17285,7 +17264,7 @@
       <c r="I70" s="29"/>
       <c r="J70" s="29"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="35">
@@ -17305,7 +17284,7 @@
       <c r="I71" s="29"/>
       <c r="J71" s="29"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="38">
@@ -17325,7 +17304,7 @@
       <c r="I72" s="29"/>
       <c r="J72" s="29"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="35">
@@ -17345,7 +17324,7 @@
       <c r="I73" s="29"/>
       <c r="J73" s="29"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="38">
@@ -17365,7 +17344,7 @@
       <c r="I74" s="29"/>
       <c r="J74" s="29"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="35">
@@ -17385,7 +17364,7 @@
       <c r="I75" s="29"/>
       <c r="J75" s="29"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="38">
@@ -17405,7 +17384,7 @@
       <c r="I76" s="29"/>
       <c r="J76" s="29"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="35">
@@ -17425,7 +17404,7 @@
       <c r="I77" s="29"/>
       <c r="J77" s="29"/>
     </row>
-    <row r="78" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="38">
@@ -17445,7 +17424,7 @@
       <c r="I78" s="29"/>
       <c r="J78" s="29"/>
     </row>
-    <row r="79" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="35">
@@ -17465,7 +17444,7 @@
       <c r="I79" s="29"/>
       <c r="J79" s="29"/>
     </row>
-    <row r="80" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="38">
@@ -17485,7 +17464,7 @@
       <c r="I80" s="29"/>
       <c r="J80" s="29"/>
     </row>
-    <row r="81" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="35">
@@ -17505,7 +17484,7 @@
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
     </row>
-    <row r="82" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="38">
@@ -17525,7 +17504,7 @@
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
     </row>
-    <row r="83" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="35">
@@ -17545,7 +17524,7 @@
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
     </row>
-    <row r="84" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="38">
@@ -17565,7 +17544,7 @@
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
     </row>
-    <row r="85" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="35">
@@ -17585,7 +17564,7 @@
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
     </row>
-    <row r="86" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="38">
@@ -17605,7 +17584,7 @@
       <c r="I86" s="29"/>
       <c r="J86" s="29"/>
     </row>
-    <row r="87" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="35">
@@ -17625,7 +17604,7 @@
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
     </row>
-    <row r="88" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="38">
@@ -17645,7 +17624,7 @@
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
     </row>
-    <row r="89" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="35">
@@ -17665,7 +17644,7 @@
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
     </row>
-    <row r="90" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="38">
@@ -17685,7 +17664,7 @@
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
     </row>
-    <row r="91" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="35">
@@ -17705,7 +17684,7 @@
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
     </row>
-    <row r="92" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="38">
@@ -17725,7 +17704,7 @@
       <c r="I92" s="29"/>
       <c r="J92" s="29"/>
     </row>
-    <row r="93" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="35">
@@ -17745,7 +17724,7 @@
       <c r="I93" s="29"/>
       <c r="J93" s="29"/>
     </row>
-    <row r="94" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="38">
@@ -17765,7 +17744,7 @@
       <c r="I94" s="29"/>
       <c r="J94" s="29"/>
     </row>
-    <row r="95" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="35">
@@ -17785,7 +17764,7 @@
       <c r="I95" s="29"/>
       <c r="J95" s="29"/>
     </row>
-    <row r="96" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="38">
@@ -17805,7 +17784,7 @@
       <c r="I96" s="29"/>
       <c r="J96" s="29"/>
     </row>
-    <row r="97" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="35">
@@ -17825,7 +17804,7 @@
       <c r="I97" s="29"/>
       <c r="J97" s="29"/>
     </row>
-    <row r="98" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="38">
@@ -17845,7 +17824,7 @@
       <c r="I98" s="29"/>
       <c r="J98" s="29"/>
     </row>
-    <row r="99" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="35">
@@ -17865,7 +17844,7 @@
       <c r="I99" s="29"/>
       <c r="J99" s="29"/>
     </row>
-    <row r="100" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="38">
@@ -17885,7 +17864,7 @@
       <c r="I100" s="29"/>
       <c r="J100" s="29"/>
     </row>
-    <row r="101" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="35">
@@ -17905,7 +17884,7 @@
       <c r="I101" s="29"/>
       <c r="J101" s="29"/>
     </row>
-    <row r="102" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="38">
@@ -17925,7 +17904,7 @@
       <c r="I102" s="29"/>
       <c r="J102" s="29"/>
     </row>
-    <row r="103" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="35">
@@ -17945,7 +17924,7 @@
       <c r="I103" s="29"/>
       <c r="J103" s="29"/>
     </row>
-    <row r="104" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="38">
@@ -17965,7 +17944,7 @@
       <c r="I104" s="29"/>
       <c r="J104" s="29"/>
     </row>
-    <row r="105" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="35">
@@ -17985,7 +17964,7 @@
       <c r="I105" s="29"/>
       <c r="J105" s="29"/>
     </row>
-    <row r="106" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="38">
@@ -18005,7 +17984,7 @@
       <c r="I106" s="29"/>
       <c r="J106" s="29"/>
     </row>
-    <row r="107" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="35">
@@ -18025,7 +18004,7 @@
       <c r="I107" s="29"/>
       <c r="J107" s="29"/>
     </row>
-    <row r="108" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="38">
@@ -18045,7 +18024,7 @@
       <c r="I108" s="29"/>
       <c r="J108" s="29"/>
     </row>
-    <row r="109" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="35">
@@ -18065,7 +18044,7 @@
       <c r="I109" s="29"/>
       <c r="J109" s="29"/>
     </row>
-    <row r="110" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="38">
@@ -18085,7 +18064,7 @@
       <c r="I110" s="29"/>
       <c r="J110" s="29"/>
     </row>
-    <row r="111" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="35">
@@ -18105,7 +18084,7 @@
       <c r="I111" s="29"/>
       <c r="J111" s="29"/>
     </row>
-    <row r="112" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="38">
@@ -18125,7 +18104,7 @@
       <c r="I112" s="29"/>
       <c r="J112" s="29"/>
     </row>
-    <row r="113" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="35">
@@ -18145,7 +18124,7 @@
       <c r="I113" s="29"/>
       <c r="J113" s="29"/>
     </row>
-    <row r="114" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="38">
@@ -18165,7 +18144,7 @@
       <c r="I114" s="29"/>
       <c r="J114" s="29"/>
     </row>
-    <row r="115" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="35">
@@ -18185,7 +18164,7 @@
       <c r="I115" s="29"/>
       <c r="J115" s="29"/>
     </row>
-    <row r="116" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="38">
@@ -18205,7 +18184,7 @@
       <c r="I116" s="29"/>
       <c r="J116" s="29"/>
     </row>
-    <row r="117" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="35">
@@ -18225,7 +18204,7 @@
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
     </row>
-    <row r="118" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="38">
@@ -18245,7 +18224,7 @@
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
     </row>
-    <row r="119" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="35">
@@ -18265,7 +18244,7 @@
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
     </row>
-    <row r="120" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="38">
@@ -18285,7 +18264,7 @@
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
     </row>
-    <row r="121" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="35">
@@ -18305,7 +18284,7 @@
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
     </row>
-    <row r="122" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="38">
@@ -18325,7 +18304,7 @@
       <c r="I122" s="29"/>
       <c r="J122" s="29"/>
     </row>
-    <row r="123" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="35">
@@ -18345,7 +18324,7 @@
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
     </row>
-    <row r="124" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="38">
@@ -18365,7 +18344,7 @@
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
     </row>
-    <row r="125" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="35">
@@ -18385,7 +18364,7 @@
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
     </row>
-    <row r="126" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="38">
@@ -18405,7 +18384,7 @@
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
     </row>
-    <row r="127" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="35">
@@ -18425,7 +18404,7 @@
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
     </row>
-    <row r="128" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="38">
@@ -18445,7 +18424,7 @@
       <c r="I128" s="29"/>
       <c r="J128" s="29"/>
     </row>
-    <row r="129" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="35">
@@ -18465,7 +18444,7 @@
       <c r="I129" s="29"/>
       <c r="J129" s="29"/>
     </row>
-    <row r="130" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="38">
@@ -18485,7 +18464,7 @@
       <c r="I130" s="29"/>
       <c r="J130" s="29"/>
     </row>
-    <row r="131" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="35">
@@ -18505,7 +18484,7 @@
       <c r="I131" s="29"/>
       <c r="J131" s="29"/>
     </row>
-    <row r="132" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="38">
@@ -18525,7 +18504,7 @@
       <c r="I132" s="29"/>
       <c r="J132" s="29"/>
     </row>
-    <row r="133" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:10" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="29"/>
       <c r="B133" s="27"/>
       <c r="C133" s="35">
@@ -18545,7 +18524,7 @@
       <c r="I133" s="29"/>
       <c r="J133" s="29"/>
     </row>
-    <row r="134" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="38">
         <v>76</v>
       </c>
@@ -18559,7 +18538,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="35">
         <v>77</v>
       </c>
@@ -18573,7 +18552,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="3">
         <v>78</v>
       </c>
@@ -18587,7 +18566,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>79</v>
       </c>
@@ -18601,7 +18580,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="3">
         <v>80</v>
       </c>
@@ -18615,7 +18594,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C139" s="3">
         <v>81</v>
       </c>
@@ -18652,29 +18631,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R139"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>267</v>
       </c>
@@ -18682,7 +18661,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -18690,7 +18669,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>70</v>
@@ -18698,7 +18677,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>15</v>
@@ -18706,13 +18685,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>70</v>
       </c>
@@ -18720,7 +18699,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>6</v>
@@ -18735,7 +18714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -18749,7 +18728,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -18763,7 +18742,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -18777,7 +18756,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -18791,7 +18770,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -18805,7 +18784,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -18819,7 +18798,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -18833,7 +18812,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -18847,7 +18826,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -18861,7 +18840,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -18875,7 +18854,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -18889,7 +18868,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -18903,7 +18882,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -18917,7 +18896,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -18931,7 +18910,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -18945,7 +18924,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -18959,7 +18938,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -18973,7 +18952,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -18987,7 +18966,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -19001,7 +18980,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -19015,7 +18994,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -19029,7 +19008,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -19043,7 +19022,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -19057,7 +19036,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -19071,7 +19050,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -19085,7 +19064,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -19099,7 +19078,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -19113,7 +19092,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -19127,7 +19106,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -19141,7 +19120,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -19155,7 +19134,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -19169,7 +19148,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -19183,7 +19162,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -19197,7 +19176,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -19211,7 +19190,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -19225,7 +19204,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -19239,7 +19218,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -19253,7 +19232,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -19267,7 +19246,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -19281,7 +19260,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -19295,7 +19274,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -19309,7 +19288,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -19323,7 +19302,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -19337,7 +19316,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -19351,7 +19330,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -19365,7 +19344,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -19379,7 +19358,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -19393,12 +19372,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="33" t="s">
         <v>6</v>
       </c>
@@ -19412,7 +19391,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="35">
         <v>1</v>
       </c>
@@ -19426,7 +19405,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="38">
         <v>2</v>
       </c>
@@ -19440,7 +19419,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="35">
         <v>3</v>
       </c>
@@ -19454,7 +19433,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="38">
         <v>4</v>
       </c>
@@ -19468,7 +19447,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="35">
         <v>5</v>
       </c>
@@ -19482,7 +19461,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="38">
         <v>6</v>
       </c>
@@ -19496,7 +19475,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="35">
@@ -19517,7 +19496,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="38">
@@ -19538,7 +19517,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="35">
@@ -19559,7 +19538,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="38">
@@ -19580,7 +19559,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="35">
@@ -19601,7 +19580,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="38">
@@ -19622,7 +19601,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="35">
@@ -19643,7 +19622,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="38">
@@ -19664,7 +19643,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="35">
@@ -19685,7 +19664,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="38">
@@ -19706,7 +19685,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="35">
@@ -19727,7 +19706,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="38">
@@ -19748,7 +19727,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="35">
@@ -19769,7 +19748,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="38">
@@ -19790,7 +19769,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="35">
@@ -19811,7 +19790,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="38">
@@ -19832,7 +19811,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="35">
@@ -19853,7 +19832,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="38">
@@ -19874,7 +19853,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="35">
@@ -19895,7 +19874,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="38">
@@ -19916,7 +19895,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="35">
@@ -19937,7 +19916,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="38">
@@ -19958,7 +19937,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="35">
@@ -19979,7 +19958,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="38">
@@ -20000,7 +19979,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="35">
@@ -20021,7 +20000,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="38">
@@ -20042,7 +20021,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="35">
@@ -20063,7 +20042,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="38">
@@ -20084,7 +20063,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="35">
@@ -20105,7 +20084,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="38">
@@ -20126,7 +20105,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="35">
@@ -20147,7 +20126,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="38">
@@ -20168,7 +20147,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="35">
@@ -20189,7 +20168,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="38">
@@ -20210,7 +20189,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="35">
@@ -20231,7 +20210,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="38">
@@ -20252,7 +20231,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="35">
@@ -20273,7 +20252,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="38">
@@ -20294,7 +20273,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="35">
@@ -20315,7 +20294,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="38">
@@ -20336,7 +20315,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="35">
@@ -20357,7 +20336,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="38">
@@ -20378,7 +20357,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="35">
@@ -20399,7 +20378,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="38">
@@ -20420,7 +20399,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="35">
@@ -20441,7 +20420,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="38">
@@ -20462,7 +20441,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="35">
@@ -20483,7 +20462,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="38">
@@ -20504,7 +20483,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="35">
@@ -20525,7 +20504,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="38">
@@ -20546,7 +20525,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="35">
@@ -20567,7 +20546,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="38">
@@ -20588,7 +20567,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="35">
@@ -20609,7 +20588,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="38">
@@ -20630,7 +20609,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="35">
@@ -20651,7 +20630,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="38">
@@ -20672,7 +20651,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="35">
@@ -20693,7 +20672,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="38">
@@ -20714,7 +20693,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="35">
@@ -20735,7 +20714,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="38">
@@ -20756,7 +20735,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="35">
@@ -20777,7 +20756,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="38">
@@ -20798,7 +20777,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="35">
@@ -20819,7 +20798,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="38">
@@ -20840,7 +20819,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="35">
@@ -20861,7 +20840,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="38">
@@ -20882,7 +20861,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="35">
@@ -20903,7 +20882,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="38">
@@ -20924,7 +20903,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="29"/>
       <c r="B133" s="27"/>
       <c r="C133" s="35">
@@ -20945,7 +20924,7 @@
       <c r="J133" s="29"/>
       <c r="K133" s="29"/>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="38">
         <v>76</v>
       </c>
@@ -20959,7 +20938,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="35">
         <v>77</v>
       </c>
@@ -20973,7 +20952,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="3">
         <v>78</v>
       </c>
@@ -20987,7 +20966,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="35">
         <v>79</v>
       </c>
@@ -21001,7 +20980,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="3">
         <v>80</v>
       </c>
@@ -21015,7 +20994,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C139" s="35">
         <v>81</v>
       </c>
